--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sba16\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0773745-6479-45F1-B92F-2DBDE1DB782D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134ED7D2-CFEF-4B35-80A6-7189B914AFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>0,01 -0,05</t>
+  </si>
+  <si>
+    <t>0,097 °C</t>
+  </si>
+  <si>
+    <t>5,646 °C</t>
   </si>
 </sst>
 </file>
@@ -454,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -493,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -517,6 +523,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -535,9 +545,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -575,7 +585,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -681,7 +691,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -823,7 +833,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -938,10 +948,18 @@
       <c r="C8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.7000000000000001E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
@@ -949,10 +967,18 @@
       <c r="C9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="29">
+        <v>0.18426999999999999</v>
+      </c>
+      <c r="E9" s="28">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134ED7D2-CFEF-4B35-80A6-7189B914AFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CDDBB4-549F-4F72-8A75-E40603AC387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="10275" yWindow="0" windowWidth="10290" windowHeight="10905" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -63,9 +63,6 @@
     <t>Temp_schatten_C</t>
   </si>
   <si>
-    <t>Temp_sonne_C</t>
-  </si>
-  <si>
     <t>RelLF_percent</t>
   </si>
   <si>
@@ -115,6 +112,12 @@
   </si>
   <si>
     <t>5,646 °C</t>
+  </si>
+  <si>
+    <t>0,28 °C</t>
+  </si>
+  <si>
+    <t>5,259 °C</t>
   </si>
 </sst>
 </file>
@@ -146,15 +149,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -389,10 +398,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -405,19 +414,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -454,13 +450,35 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -489,16 +507,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,19 +552,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -841,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
@@ -855,24 +892,24 @@
     </row>
     <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="E2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="E2" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>15</v>
+      <c r="C3" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
@@ -881,155 +918,163 @@
         <v>8</v>
       </c>
       <c r="G3" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G4" s="23">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="28"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="24" t="s">
+      <c r="F7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="19">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="G9" s="20">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="28"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="22">
+        <v>0.18426999999999999</v>
+      </c>
+      <c r="E10" s="18">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="20">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="G11" s="21">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="15" t="s">
+      <c r="C12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="15" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="8">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1.7000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0.18426999999999999</v>
-      </c>
-      <c r="E9" s="28">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="G9" s="4">
-        <v>4.3999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="G10" s="6">
-        <v>6.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="17" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1037,49 +1082,60 @@
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="17" t="s">
-        <v>13</v>
+      <c r="A14" s="28"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="15" t="s">
+        <v>11</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23"/>
-      <c r="B15" s="27"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="28"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="D16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="4:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CDDBB4-549F-4F72-8A75-E40603AC387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AAA659-2549-497D-AA8C-F25AA853A5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10275" yWindow="0" windowWidth="10290" windowHeight="10905" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -84,9 +84,6 @@
     <t>SD Originaldaten</t>
   </si>
   <si>
-    <t>3,378 °C</t>
-  </si>
-  <si>
     <t>Streuung der Originaldaten um ihren Mittelwert</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>Normierter Fehler = Wie groß der Fehler im Vergleich zur natürlichen Variabilität ist</t>
   </si>
   <si>
-    <t>10,622 °C</t>
-  </si>
-  <si>
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
@@ -111,13 +105,22 @@
     <t>0,097 °C</t>
   </si>
   <si>
-    <t>5,646 °C</t>
-  </si>
-  <si>
     <t>0,28 °C</t>
   </si>
   <si>
-    <t>5,259 °C</t>
+    <t>0,275 °C</t>
+  </si>
+  <si>
+    <t>0,138 °C</t>
+  </si>
+  <si>
+    <t>0,15 °C</t>
+  </si>
+  <si>
+    <t>0,735 °C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noch nicht durchgeführt, keine guten Korrelationswerte </t>
   </si>
 </sst>
 </file>
@@ -149,19 +152,13 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="24">
     <border>
@@ -478,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -516,15 +513,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -535,6 +523,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -878,27 +869,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="7" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="E2" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -921,75 +912,83 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="20">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="31"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="32"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="23">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F5" s="21">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G5" s="22">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="33" t="s">
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G6" s="6">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="19">
+        <v>24</v>
+      </c>
+      <c r="G7" s="8">
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="33"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
@@ -997,82 +996,85 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="33"/>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2">
         <v>2E-3</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="4">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="33"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="22">
-        <v>0.18426999999999999</v>
-      </c>
+      <c r="D10" s="19"/>
       <c r="E10" s="18">
         <v>8.0999999999999996E-3</v>
       </c>
       <c r="F10" s="2">
         <v>0.01</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="4">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
-      <c r="B11" s="34"/>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="5">
         <v>1E-3</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="6">
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="33"/>
+      <c r="E12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="15" t="s">
         <v>10</v>
       </c>
@@ -1080,52 +1082,73 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="33"/>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="33"/>
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="26"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29"/>
-      <c r="B16" s="34"/>
+      <c r="E15" s="18">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3.6999999999999998E-2</v>
+      </c>
     </row>
     <row r="17" spans="4:7" ht="105" x14ac:dyDescent="0.25">
       <c r="D17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AAA659-2549-497D-AA8C-F25AA853A5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AC6500-385A-43F6-800C-FA58EDED7868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -51,9 +51,6 @@
     <t>RMSE</t>
   </si>
   <si>
-    <t>SD von RMSE</t>
-  </si>
-  <si>
     <t>Temp_Sonne_C</t>
   </si>
   <si>
@@ -78,49 +75,28 @@
     <t>0,59 °C</t>
   </si>
   <si>
-    <t>0,24 °C</t>
-  </si>
-  <si>
-    <t>SD Originaldaten</t>
-  </si>
-  <si>
-    <t>Streuung der Originaldaten um ihren Mittelwert</t>
-  </si>
-  <si>
-    <t>wie stark die RMSE-Werte zwischen den 5 Wieder-holungen schwanken</t>
-  </si>
-  <si>
-    <t>Normierter Fehler = Wie groß der Fehler im Vergleich zur natürlichen Variabilität ist</t>
-  </si>
-  <si>
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
-    <t>ändern sich leicht, je nach Durchlauf</t>
-  </si>
-  <si>
-    <t>0,01 -0,05</t>
-  </si>
-  <si>
-    <t>0,097 °C</t>
-  </si>
-  <si>
-    <t>0,28 °C</t>
-  </si>
-  <si>
-    <t>0,275 °C</t>
-  </si>
-  <si>
-    <t>0,138 °C</t>
-  </si>
-  <si>
-    <t>0,15 °C</t>
-  </si>
-  <si>
-    <t>0,735 °C</t>
-  </si>
-  <si>
     <t xml:space="preserve">noch nicht durchgeführt, keine guten Korrelationswerte </t>
+  </si>
+  <si>
+    <t>1,31 °C</t>
+  </si>
+  <si>
+    <t>Spannweite</t>
+  </si>
+  <si>
+    <t>Standardabweichung</t>
+  </si>
+  <si>
+    <t>0,45 °C</t>
+  </si>
+  <si>
+    <t>0,22 °C</t>
+  </si>
+  <si>
+    <t>0,6 °C</t>
   </si>
 </sst>
 </file>
@@ -152,15 +128,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -197,7 +191,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -206,6 +215,36 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -215,116 +254,26 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -382,7 +331,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -398,19 +347,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -469,13 +405,168 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -484,76 +575,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,296 +1036,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="7" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="8" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="40"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E5" s="32">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F5" s="45">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.114</v>
+      </c>
+      <c r="H5" s="45">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="53">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="E6" s="54">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="F6" s="46">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="H6" s="46">
+        <v>0.19500000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="33">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F7" s="43">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="H7" s="43">
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E8" s="34">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="F8" s="42">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.123</v>
+      </c>
+      <c r="H8" s="42">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="18"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="47"/>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="35">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="47">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="H10" s="47">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="50">
+        <v>1.8120000000000001E-2</v>
+      </c>
+      <c r="E11" s="44">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F11" s="47">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H11" s="47">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="33">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F12" s="43">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="H12" s="43">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="42"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="47"/>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="47"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="15" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="47"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="23">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F5" s="21">
-        <v>2.7E-2</v>
-      </c>
-      <c r="G5" s="22">
-        <v>9.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G6" s="6">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
+      <c r="D17" s="5"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="43"/>
+    </row>
+    <row r="18" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="D18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="8">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1.7000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="G10" s="4">
-        <v>4.3999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="G11" s="6">
-        <v>6.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="7">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.10199999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="4"/>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="18">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>4.7E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G16" s="6">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B16"/>
+  <mergeCells count="13">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AC6500-385A-43F6-800C-FA58EDED7868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AAA659-2549-497D-AA8C-F25AA853A5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -51,6 +51,9 @@
     <t>RMSE</t>
   </si>
   <si>
+    <t>SD von RMSE</t>
+  </si>
+  <si>
     <t>Temp_Sonne_C</t>
   </si>
   <si>
@@ -75,28 +78,49 @@
     <t>0,59 °C</t>
   </si>
   <si>
+    <t>0,24 °C</t>
+  </si>
+  <si>
+    <t>SD Originaldaten</t>
+  </si>
+  <si>
+    <t>Streuung der Originaldaten um ihren Mittelwert</t>
+  </si>
+  <si>
+    <t>wie stark die RMSE-Werte zwischen den 5 Wieder-holungen schwanken</t>
+  </si>
+  <si>
+    <t>Normierter Fehler = Wie groß der Fehler im Vergleich zur natürlichen Variabilität ist</t>
+  </si>
+  <si>
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
+    <t>ändern sich leicht, je nach Durchlauf</t>
+  </si>
+  <si>
+    <t>0,01 -0,05</t>
+  </si>
+  <si>
+    <t>0,097 °C</t>
+  </si>
+  <si>
+    <t>0,28 °C</t>
+  </si>
+  <si>
+    <t>0,275 °C</t>
+  </si>
+  <si>
+    <t>0,138 °C</t>
+  </si>
+  <si>
+    <t>0,15 °C</t>
+  </si>
+  <si>
+    <t>0,735 °C</t>
+  </si>
+  <si>
     <t xml:space="preserve">noch nicht durchgeführt, keine guten Korrelationswerte </t>
-  </si>
-  <si>
-    <t>1,31 °C</t>
-  </si>
-  <si>
-    <t>Spannweite</t>
-  </si>
-  <si>
-    <t>Standardabweichung</t>
-  </si>
-  <si>
-    <t>0,45 °C</t>
-  </si>
-  <si>
-    <t>0,22 °C</t>
-  </si>
-  <si>
-    <t>0,6 °C</t>
   </si>
 </sst>
 </file>
@@ -128,33 +152,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="33">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -191,6 +197,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -279,6 +300,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -331,7 +382,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -347,6 +398,19 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -405,168 +469,13 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -575,152 +484,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1036,327 +869,296 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
-    <col min="5" max="8" width="9.42578125" customWidth="1"/>
+    <col min="3" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="7" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="E2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G4" s="20">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="23">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F5" s="21">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G5" s="22">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="31"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="39" t="s">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G6" s="6">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="8">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="18">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="G11" s="6">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="4"/>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="26"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="18">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="D17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41" t="s">
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="40"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="32">
-        <v>1.9E-2</v>
-      </c>
-      <c r="F5" s="45">
-        <v>1.9E-2</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.114</v>
-      </c>
-      <c r="H5" s="45">
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="53">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="E6" s="54">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="F6" s="46">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="H6" s="46">
-        <v>0.19500000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="33">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="F7" s="43">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="H7" s="43">
-        <v>0.14299999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="34">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="F8" s="42">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.123</v>
-      </c>
-      <c r="H8" s="42">
-        <v>0.123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="47"/>
-      <c r="I9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="35">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F10" s="47">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="G10" s="4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="H10" s="47">
-        <v>3.9E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="50">
-        <v>1.8120000000000001E-2</v>
-      </c>
-      <c r="E11" s="44">
-        <v>2.4E-2</v>
-      </c>
-      <c r="F11" s="47">
-        <v>2.4E-2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="H11" s="47">
-        <v>9.8000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="49" t="s">
+      <c r="G17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="33">
-        <v>1.9E-2</v>
-      </c>
-      <c r="F12" s="43">
-        <v>1.9E-2</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="H12" s="43">
-        <v>0.13400000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="42"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="47"/>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="47"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="47"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="43"/>
-    </row>
-    <row r="18" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="D18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+  <mergeCells count="6">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AAA659-2549-497D-AA8C-F25AA853A5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE4CD5A-D33E-4D5A-9E96-79FD2882D24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
   </si>
@@ -51,9 +62,6 @@
     <t>RMSE</t>
   </si>
   <si>
-    <t>SD von RMSE</t>
-  </si>
-  <si>
     <t>Temp_Sonne_C</t>
   </si>
   <si>
@@ -75,52 +83,58 @@
     <t>NRMSE</t>
   </si>
   <si>
-    <t>0,59 °C</t>
-  </si>
-  <si>
-    <t>0,24 °C</t>
-  </si>
-  <si>
-    <t>SD Originaldaten</t>
-  </si>
-  <si>
-    <t>Streuung der Originaldaten um ihren Mittelwert</t>
-  </si>
-  <si>
-    <t>wie stark die RMSE-Werte zwischen den 5 Wieder-holungen schwanken</t>
-  </si>
-  <si>
-    <t>Normierter Fehler = Wie groß der Fehler im Vergleich zur natürlichen Variabilität ist</t>
-  </si>
-  <si>
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
-    <t>ändern sich leicht, je nach Durchlauf</t>
-  </si>
-  <si>
-    <t>0,01 -0,05</t>
-  </si>
-  <si>
-    <t>0,097 °C</t>
-  </si>
-  <si>
-    <t>0,28 °C</t>
-  </si>
-  <si>
-    <t>0,275 °C</t>
-  </si>
-  <si>
-    <t>0,138 °C</t>
-  </si>
-  <si>
-    <t>0,15 °C</t>
-  </si>
-  <si>
-    <t>0,735 °C</t>
-  </si>
-  <si>
     <t xml:space="preserve">noch nicht durchgeführt, keine guten Korrelationswerte </t>
+  </si>
+  <si>
+    <t>Spannweite</t>
+  </si>
+  <si>
+    <t>Standardabweichung</t>
+  </si>
+  <si>
+    <t>0,6 °C</t>
+  </si>
+  <si>
+    <t>1,29 °C</t>
+  </si>
+  <si>
+    <t>0,22 °C</t>
+  </si>
+  <si>
+    <t>0,45 °C</t>
+  </si>
+  <si>
+    <t>0,58 °C</t>
+  </si>
+  <si>
+    <t>Größe des Fehlers im Verhältnis zur Variabilität der Daten</t>
+  </si>
+  <si>
+    <t>Fehler beträgt x % der gesamten Spannweite der Daten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehler relativ zur typischen Streuung der Daten </t>
+  </si>
+  <si>
+    <t>=wie stark das Model im Durchschnitt vom Mittelwert abweicht, imVerhältnis zur normalen Variabilität der Messwerte</t>
+  </si>
+  <si>
+    <t>1,49 °C</t>
+  </si>
+  <si>
+    <t>Überarbeitung notwendig</t>
+  </si>
+  <si>
+    <t>0,3 °C</t>
+  </si>
+  <si>
+    <t>0,35 °C</t>
+  </si>
+  <si>
+    <t>Modellfehler ist im Mittel ca. x % der Daten</t>
   </si>
 </sst>
 </file>
@@ -152,15 +166,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -215,36 +247,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -300,37 +302,77 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -341,76 +383,128 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -421,16 +515,61 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -440,33 +579,22 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -475,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -484,76 +612,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,296 +1050,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="7" width="13.42578125" customWidth="1"/>
+    <col min="5" max="8" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="E2" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="H4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F5" s="21">
+        <f>E5</f>
+        <v>1.9E-2</v>
+      </c>
+      <c r="G5" s="25">
+        <v>0.114</v>
+      </c>
+      <c r="H5" s="23">
+        <f>G5</f>
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="43">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="E6" s="39">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" ref="F6:F17" si="0">E6</f>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="H6" s="47">
+        <f t="shared" ref="H6:H17" si="1">G6</f>
+        <v>0.19400000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F7" s="20">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="H7" s="22">
+        <f t="shared" si="1"/>
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="D8" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G8" s="28">
+        <v>0.123</v>
+      </c>
+      <c r="H8" s="23">
+        <f t="shared" si="1"/>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="45"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G10" s="29">
+        <v>3.9E-2</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="1"/>
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="41">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="G11" s="29">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H11" s="36">
+        <f t="shared" si="1"/>
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F12" s="20">
+        <f t="shared" si="0"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="G12" s="27">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="H12" s="22">
+        <f t="shared" si="1"/>
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="H13" s="48">
+        <f t="shared" si="1"/>
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G15" s="29">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="1"/>
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="49">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="G16" s="29">
+        <v>0.104</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="1"/>
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F17" s="20">
+        <f t="shared" si="0"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G17" s="27">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="H17" s="22">
+        <f t="shared" si="1"/>
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="D18" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11" t="s">
+      <c r="E18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="23">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F5" s="21">
-        <v>2.7E-2</v>
-      </c>
-      <c r="G5" s="22">
-        <v>9.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G6" s="6">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="8">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1.7000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="G10" s="4">
-        <v>4.3999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="G11" s="6">
-        <v>6.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="7">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.10199999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="4"/>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="18">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>4.7E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G16" s="6">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>21</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B16"/>
+  <mergeCells count="11">
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE4CD5A-D33E-4D5A-9E96-79FD2882D24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9495F72A-B80B-4109-B621-1759254DA3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
-    <t xml:space="preserve">Mittels Modell erzeugte Daten </t>
-  </si>
-  <si>
     <t>Meusebach trocken</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>Messgrößen</t>
   </si>
   <si>
-    <t>NRMSE</t>
-  </si>
-  <si>
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
@@ -95,21 +89,6 @@
     <t>Standardabweichung</t>
   </si>
   <si>
-    <t>0,6 °C</t>
-  </si>
-  <si>
-    <t>1,29 °C</t>
-  </si>
-  <si>
-    <t>0,22 °C</t>
-  </si>
-  <si>
-    <t>0,45 °C</t>
-  </si>
-  <si>
-    <t>0,58 °C</t>
-  </si>
-  <si>
     <t>Größe des Fehlers im Verhältnis zur Variabilität der Daten</t>
   </si>
   <si>
@@ -122,19 +101,40 @@
     <t>=wie stark das Model im Durchschnitt vom Mittelwert abweicht, imVerhältnis zur normalen Variabilität der Messwerte</t>
   </si>
   <si>
-    <t>1,49 °C</t>
-  </si>
-  <si>
-    <t>Überarbeitung notwendig</t>
-  </si>
-  <si>
-    <t>0,3 °C</t>
-  </si>
-  <si>
-    <t>0,35 °C</t>
-  </si>
-  <si>
     <t>Modellfehler ist im Mittel ca. x % der Daten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>1,27 °C</t>
+  </si>
+  <si>
+    <t>0,44 °C</t>
+  </si>
+  <si>
+    <t>0,21 °C</t>
+  </si>
+  <si>
+    <t>0,50 °C</t>
+  </si>
+  <si>
+    <t>0,53 °C</t>
+  </si>
+  <si>
+    <t>0,25 °C</t>
+  </si>
+  <si>
+    <t>0,33 °C</t>
+  </si>
+  <si>
+    <t>1,14 °C</t>
+  </si>
+  <si>
+    <t>NRMSE berechnet mittels …</t>
   </si>
 </sst>
 </file>
@@ -166,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,18 +181,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -224,21 +218,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -511,6 +490,119 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -518,92 +610,16 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -612,63 +628,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -683,57 +664,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1059,404 +1080,399 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="39"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="35"/>
+      <c r="G4" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="37"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="C5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F5" s="8">
+        <f>E5</f>
+        <v>1.6E-2</v>
+      </c>
+      <c r="G5" s="11">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H5" s="49">
+        <f>G5</f>
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="41">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="E6" s="21">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" ref="F6:F17" si="0">E6</f>
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.161</v>
+      </c>
+      <c r="H6" s="22">
+        <f>G6</f>
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="48">
+        <f t="shared" ref="H6:H17" si="1">G7</f>
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="34"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="35"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1.9E-2</v>
-      </c>
-      <c r="F5" s="21">
-        <f>E5</f>
-        <v>1.9E-2</v>
-      </c>
-      <c r="G5" s="25">
-        <v>0.114</v>
-      </c>
-      <c r="H5" s="23">
-        <f>G5</f>
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="43">
-        <v>3.1199999999999999E-2</v>
-      </c>
-      <c r="E6" s="39">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" ref="F6:F17" si="0">E6</f>
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="G6" s="26">
-        <v>0.19400000000000001</v>
-      </c>
-      <c r="H6" s="47">
-        <f t="shared" ref="H6:H17" si="1">G6</f>
-        <v>0.19400000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="F7" s="20">
-        <f t="shared" si="0"/>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="H7" s="22">
-        <f t="shared" si="1"/>
-        <v>0.14299999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>20</v>
+      <c r="D8" s="43" t="s">
+        <v>24</v>
       </c>
       <c r="E8" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="8">
         <f t="shared" si="0"/>
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G8" s="28">
-        <v>0.123</v>
-      </c>
-      <c r="H8" s="23">
+      <c r="G8" s="14">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="H8" s="47">
         <f t="shared" si="1"/>
-        <v>0.123</v>
+        <v>0.11899999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="45"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="44"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="24">
+      <c r="G9" s="15"/>
+      <c r="H9" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="31" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G10" s="15">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="D11" s="45">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="G10" s="29">
-        <v>3.9E-2</v>
-      </c>
-      <c r="H10" s="24">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G11" s="15">
+        <v>9.4E-2</v>
+      </c>
+      <c r="H11" s="20">
         <f t="shared" si="1"/>
-        <v>3.9E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="31" t="s">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="41">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="E11" s="40">
-        <v>2.4E-2</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D12" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
-        <v>2.4E-2</v>
-      </c>
-      <c r="G11" s="29">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="H12" s="48">
+        <f t="shared" si="1"/>
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="0"/>
+        <v>2.3E-2</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0.158</v>
+      </c>
+      <c r="H13" s="23">
+        <f t="shared" si="1"/>
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="44"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     </v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="0"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G15" s="15">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="46">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="0"/>
+        <v>2.3E-2</v>
+      </c>
+      <c r="G16" s="15">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H16" s="50">
         <f t="shared" si="1"/>
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1.9E-2</v>
-      </c>
-      <c r="F12" s="20">
-        <f t="shared" si="0"/>
-        <v>1.9E-2</v>
-      </c>
-      <c r="G12" s="27">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="H12" s="22">
-        <f t="shared" si="1"/>
-        <v>0.13400000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="F13" s="21">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="G13" s="28">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="H13" s="48">
-        <f t="shared" si="1"/>
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="I13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="42" t="s">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="42" t="s">
         <v>30</v>
-      </c>
-      <c r="E15" s="2">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="F15" s="7">
-        <f t="shared" si="0"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="G15" s="29">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="H15" s="24">
-        <f t="shared" si="1"/>
-        <v>5.7000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="49">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="E16" s="40">
-        <v>2.4E-2</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="0"/>
-        <v>2.4E-2</v>
-      </c>
-      <c r="G16" s="29">
-        <v>0.104</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="1"/>
-        <v>0.104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="E17" s="4">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="7">
         <f t="shared" si="0"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G17" s="27">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="G17" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="H17" s="9">
         <f t="shared" si="1"/>
-        <v>8.4000000000000005E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="D18" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9495F72A-B80B-4109-B621-1759254DA3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF872017-A69D-4A2C-A95F-5ED4A113557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Meusebach trocken</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Abweichung der mittels des Modells erzeugten Werte von Originalen</t>
   </si>
   <si>
-    <t xml:space="preserve">noch nicht durchgeführt, keine guten Korrelationswerte </t>
-  </si>
-  <si>
     <t>Spannweite</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
     <t>1,27 °C</t>
   </si>
   <si>
@@ -135,6 +129,9 @@
   </si>
   <si>
     <t>NRMSE berechnet mittels …</t>
+  </si>
+  <si>
+    <t>2344 lux</t>
   </si>
 </sst>
 </file>
@@ -619,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -680,6 +677,56 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -703,59 +750,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1071,67 +1065,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="8" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="39"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="37"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="H4" s="25"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="45" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>27</v>
+      <c r="D5" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="E5" s="5">
         <v>1.6E-2</v>
@@ -1143,18 +1137,18 @@
       <c r="G5" s="11">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="35">
         <f>G5</f>
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="28"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="27">
         <v>2.5899999999999999E-2</v>
       </c>
       <c r="E6" s="21">
@@ -1172,14 +1166,14 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="29"/>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="43"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="42" t="s">
-        <v>28</v>
+      <c r="D7" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="4">
         <v>2.4E-2</v>
@@ -1191,21 +1185,21 @@
       <c r="G7" s="13">
         <v>0.13</v>
       </c>
-      <c r="H7" s="48">
-        <f t="shared" ref="H6:H17" si="1">G7</f>
+      <c r="H7" s="34">
+        <f t="shared" ref="H7:H17" si="1">G7</f>
         <v>0.13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="30" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="43"/>
+      <c r="B8" s="48" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>24</v>
+      <c r="D8" s="29" t="s">
+        <v>22</v>
       </c>
       <c r="E8" s="5">
         <v>2.1999999999999999E-2</v>
@@ -1217,40 +1211,43 @@
       <c r="G8" s="14">
         <v>0.11899999999999999</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="33">
         <f t="shared" si="1"/>
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="30"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.2000000000000001E-2</v>
+      </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="15"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.23300000000000001</v>
+      </c>
       <c r="H9" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="30"/>
+        <v>0.23300000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="48"/>
       <c r="C10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="44" t="s">
-        <v>26</v>
+      <c r="D10" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="E10" s="2">
         <v>6.0000000000000001E-3</v>
@@ -1267,13 +1264,13 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="30"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="48"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="31">
         <v>1.7299999999999999E-2</v>
       </c>
       <c r="E11" s="2">
@@ -1291,14 +1288,14 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="31"/>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="44"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>25</v>
+      <c r="D12" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="4">
         <v>1.7999999999999999E-2</v>
@@ -1310,23 +1307,23 @@
       <c r="G12" s="13">
         <v>0.13100000000000001</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="34">
         <f t="shared" si="1"/>
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="48" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>31</v>
+      <c r="D13" s="29" t="s">
+        <v>29</v>
       </c>
       <c r="E13" s="5">
         <v>2.3E-2</v>
@@ -1343,37 +1340,38 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="30"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="48"/>
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="30">
+        <v>2331</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3.2000000000000001E-2</v>
+      </c>
       <c r="F14" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="10" t="str">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="H14" s="10">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">     </v>
-      </c>
-      <c r="I14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="30"/>
+        <v>0.23200000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="B15" s="48"/>
       <c r="C15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="44" t="s">
-        <v>29</v>
+      <c r="D15" s="30" t="s">
+        <v>27</v>
       </c>
       <c r="E15" s="2">
         <v>8.0000000000000002E-3</v>
@@ -1390,13 +1388,13 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="30"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="48"/>
       <c r="C16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="32">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E16" s="2">
@@ -1409,19 +1407,19 @@
       <c r="G16" s="15">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="20">
         <f t="shared" si="1"/>
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="42" t="s">
-        <v>30</v>
+      <c r="D17" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="E17" s="4">
         <v>1.4999999999999999E-2</v>
@@ -1443,36 +1441,36 @@
         <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF872017-A69D-4A2C-A95F-5ED4A113557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B469A0-9E61-428A-8816-8B08B8E249DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>Meusebach trocken</t>
   </si>
@@ -125,13 +125,19 @@
     <t>0,33 °C</t>
   </si>
   <si>
-    <t>1,14 °C</t>
-  </si>
-  <si>
     <t>NRMSE berechnet mittels …</t>
   </si>
   <si>
-    <t>2344 lux</t>
+    <t>3290 lux</t>
+  </si>
+  <si>
+    <t>2331 lux</t>
+  </si>
+  <si>
+    <t>nochmal nacharbeiten</t>
+  </si>
+  <si>
+    <t>1,13 °C</t>
   </si>
 </sst>
 </file>
@@ -616,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -710,6 +716,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -727,29 +757,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,60 +1074,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="8" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="41" t="s">
+      <c r="E3" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="41"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="25"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
@@ -1142,9 +1151,9 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="46"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
@@ -1166,9 +1175,9 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
-      <c r="B7" s="47"/>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
@@ -1190,9 +1199,9 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="B8" s="48" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
@@ -1216,33 +1225,33 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="48"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="37"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2">
-        <v>3.2000000000000001E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
-        <v>3.2000000000000001E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="G9" s="15">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="H9" s="10">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H9" s="50">
         <f t="shared" si="1"/>
-        <v>0.23300000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
-      <c r="B10" s="48"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="37"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="17" t="s">
         <v>9</v>
       </c>
@@ -1264,9 +1273,9 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="B11" s="48"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="37"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
@@ -1288,9 +1297,9 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44"/>
-      <c r="B12" s="49"/>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="18" t="s">
         <v>11</v>
       </c>
@@ -1312,18 +1321,18 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="42" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" s="5">
         <v>2.3E-2</v>
@@ -1339,15 +1348,18 @@
         <f t="shared" si="1"/>
         <v>0.158</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="48"/>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="37"/>
+      <c r="B14" s="42"/>
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="30">
-        <v>2331</v>
+      <c r="D14" s="30" t="s">
+        <v>31</v>
       </c>
       <c r="E14" s="2">
         <v>3.2000000000000001E-2</v>
@@ -1359,14 +1371,14 @@
       <c r="G14" s="15">
         <v>0.23200000000000001</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="50">
         <f t="shared" si="1"/>
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
-      <c r="B15" s="48"/>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="37"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="17" t="s">
         <v>9</v>
       </c>
@@ -1388,9 +1400,9 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
-      <c r="B16" s="48"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="42"/>
       <c r="C16" s="17" t="s">
         <v>10</v>
       </c>
@@ -1413,8 +1425,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
-      <c r="B17" s="49"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="18" t="s">
         <v>11</v>
       </c>
@@ -1460,17 +1472,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B469A0-9E61-428A-8816-8B08B8E249DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E91CA2-CD04-47B7-8407-E76843223956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="18720" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>Meusebach trocken</t>
   </si>
@@ -104,27 +104,6 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>1,27 °C</t>
-  </si>
-  <si>
-    <t>0,44 °C</t>
-  </si>
-  <si>
-    <t>0,21 °C</t>
-  </si>
-  <si>
-    <t>0,50 °C</t>
-  </si>
-  <si>
-    <t>0,53 °C</t>
-  </si>
-  <si>
-    <t>0,25 °C</t>
-  </si>
-  <si>
-    <t>0,33 °C</t>
-  </si>
-  <si>
     <t>NRMSE berechnet mittels …</t>
   </si>
   <si>
@@ -138,6 +117,45 @@
   </si>
   <si>
     <t>1,13 °C</t>
+  </si>
+  <si>
+    <t>1,22 °C</t>
+  </si>
+  <si>
+    <t>0,45 °C</t>
+  </si>
+  <si>
+    <t>0,20 °C</t>
+  </si>
+  <si>
+    <t>0,28 °C</t>
+  </si>
+  <si>
+    <t>0,41 °C</t>
+  </si>
+  <si>
+    <t>0,26 °C</t>
+  </si>
+  <si>
+    <t>0,34 °C</t>
+  </si>
+  <si>
+    <t>Random Forest Modell</t>
+  </si>
+  <si>
+    <t>Ranger Modell (nutzt ebenfalls Random Forest, ist jedoch schneller und präziser)</t>
+  </si>
+  <si>
+    <t>1,236 °C</t>
+  </si>
+  <si>
+    <t>0,2 °C</t>
+  </si>
+  <si>
+    <t>0,095 °C</t>
+  </si>
+  <si>
+    <t>0,14 °C</t>
   </si>
 </sst>
 </file>
@@ -622,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -677,9 +695,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -706,14 +721,32 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -739,25 +772,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1074,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EA0E69-590E-4194-8C85-EDC798F433E8}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="17.5703125" customWidth="1"/>
@@ -1087,152 +1108,154 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="48"/>
+      <c r="E3" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="49" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="24" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="25"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="44" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>25</v>
+      <c r="D5" s="25" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="5">
-        <v>1.6E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="F5" s="8">
         <f>E5</f>
-        <v>1.6E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G5" s="11">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="H5" s="35">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H5" s="33">
         <f>G5</f>
-        <v>9.6000000000000002E-2</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="27">
-        <v>2.5899999999999999E-2</v>
+      <c r="D6" s="26">
+        <v>1.78E-2</v>
       </c>
       <c r="E6" s="21">
-        <v>3.7999999999999999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" ref="F6:F17" si="0">E6</f>
-        <v>3.7999999999999999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G6" s="12">
-        <v>0.161</v>
-      </c>
-      <c r="H6" s="22">
+        <v>0.111</v>
+      </c>
+      <c r="H6" s="50">
         <f>G6</f>
-        <v>0.161</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>26</v>
+      <c r="D7" s="27" t="s">
+        <v>31</v>
       </c>
       <c r="E7" s="4">
-        <v>2.4E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>2.4E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G7" s="13">
-        <v>0.13</v>
-      </c>
-      <c r="H7" s="34">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H7" s="51">
         <f t="shared" ref="H7:H17" si="1">G7</f>
-        <v>0.13</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="42"/>
+      <c r="B8" s="47" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>22</v>
+      <c r="D8" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="E8" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="0"/>
-        <v>2.1999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G8" s="14">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="H8" s="33">
+        <v>0.115</v>
+      </c>
+      <c r="H8" s="49">
         <f t="shared" si="1"/>
-        <v>0.11899999999999999</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="47"/>
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>30</v>
+      <c r="D9" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="E9" s="2">
         <v>3.3000000000000002E-2</v>
@@ -1244,19 +1267,19 @@
       <c r="G9" s="15">
         <v>0.17499999999999999</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="34">
         <f t="shared" si="1"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="42"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>24</v>
+      <c r="D10" s="29" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="2">
         <v>6.0000000000000001E-3</v>
@@ -1274,65 +1297,65 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="42"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="47"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="31">
-        <v>1.7299999999999999E-2</v>
+      <c r="D11" s="30">
+        <v>1.77E-2</v>
       </c>
       <c r="E11" s="2">
-        <v>2.1999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="0"/>
-        <v>2.1999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G11" s="15">
-        <v>9.4E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="1"/>
-        <v>9.4E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
-      <c r="B12" s="43"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="48"/>
       <c r="C12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>23</v>
+      <c r="D12" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="E12" s="4">
-        <v>1.7999999999999999E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F12" s="7">
         <f t="shared" si="0"/>
-        <v>1.7999999999999999E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G12" s="13">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="H12" s="34">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="H12" s="32">
         <f t="shared" si="1"/>
-        <v>0.13100000000000001</v>
+        <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>33</v>
+      <c r="D13" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="E13" s="5">
         <v>2.3E-2</v>
@@ -1344,22 +1367,22 @@
       <c r="G13" s="14">
         <v>0.158</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <f t="shared" si="1"/>
         <v>0.158</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="42"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="47"/>
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>31</v>
+      <c r="D14" s="29" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="2">
         <v>3.2000000000000001E-2</v>
@@ -1371,19 +1394,19 @@
       <c r="G14" s="15">
         <v>0.23200000000000001</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="34">
         <f t="shared" si="1"/>
         <v>0.23200000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
-      <c r="B15" s="42"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>27</v>
+      <c r="D15" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="E15" s="2">
         <v>8.0000000000000002E-3</v>
@@ -1393,21 +1416,21 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="G15" s="15">
-        <v>4.9000000000000002E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="H15" s="10">
         <f t="shared" si="1"/>
-        <v>4.9000000000000002E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
-      <c r="B16" s="42"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="47"/>
       <c r="C16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="32">
-        <v>1.4999999999999999E-2</v>
+      <c r="D16" s="31">
+        <v>1.54E-2</v>
       </c>
       <c r="E16" s="2">
         <v>2.3E-2</v>
@@ -1417,21 +1440,21 @@
         <v>2.3E-2</v>
       </c>
       <c r="G16" s="15">
-        <v>9.8000000000000004E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="1"/>
-        <v>9.8000000000000004E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>28</v>
+      <c r="D17" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="E17" s="4">
         <v>1.4999999999999999E-2</v>
@@ -1470,19 +1493,349 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="40"/>
+      <c r="G23" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F24" s="8">
+        <f>E24</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G24" s="11">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H24" s="33">
+        <f>G24</f>
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="42"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="26">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="E25" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" ref="F25:F36" si="2">E25</f>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G25" s="12">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="H25" s="50">
+        <f>G25</f>
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="42"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="51">
+        <f t="shared" ref="H26:H36" si="3">G26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="42"/>
+      <c r="B27" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F27" s="8">
+        <f t="shared" si="2"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="H27" s="49">
+        <f t="shared" si="3"/>
+        <v>0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="42"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="29"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="42"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="G29" s="15">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" si="3"/>
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="30">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01</v>
+      </c>
+      <c r="G30" s="15">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="H30" s="20">
+        <f t="shared" si="3"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="43"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G31" s="13">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="H31" s="51">
+        <f t="shared" si="3"/>
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="42"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="29"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="15"/>
+      <c r="H33" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="42"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="15"/>
+      <c r="H34" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="42"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="31"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="15"/>
+      <c r="H35" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="27"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="22">
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
+++ b/Logger/Modellierte_Messdaten_Fehlerstatistik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E91CA2-CD04-47B7-8407-E76843223956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7211EE-B69D-47E1-B1D8-300D7D34BDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
+    <workbookView xWindow="10005" yWindow="885" windowWidth="10485" windowHeight="9915" xr2:uid="{BC26F3C7-EBF5-411F-BEBA-61067CF8A278}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="36">
   <si>
     <t>Meusebach trocken</t>
   </si>
@@ -140,22 +140,10 @@
     <t>0,34 °C</t>
   </si>
   <si>
-    <t>Random Forest Modell</t>
-  </si>
-  <si>
     <t>Ranger Modell (nutzt ebenfalls Random Forest, ist jedoch schneller und präziser)</t>
   </si>
   <si>
-    <t>1,236 °C</t>
-  </si>
-  <si>
-    <t>0,2 °C</t>
-  </si>
-  <si>
-    <t>0,095 °C</t>
-  </si>
-  <si>
-    <t>0,14 °C</t>
+    <t>Random Forest Modell (gleiche/ ähnliche Werte bei Ranger (+ 0,1) mit Ausnahme der Licht-Modell, diese sind nicht vergleichbar)</t>
   </si>
 </sst>
 </file>
@@ -640,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -731,6 +719,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,39 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,48 +1088,48 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="40" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="40"/>
+      <c r="F4" s="48"/>
       <c r="G4" s="23" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="44" t="s">
+      <c r="A5" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
@@ -1175,13 +1154,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
-      <c r="B6" s="45"/>
+      <c r="A6" s="36"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="26">
-        <v>1.78E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="E6" s="21">
         <v>2.5999999999999999E-2</v>
@@ -1193,14 +1172,14 @@
       <c r="G6" s="12">
         <v>0.111</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="20">
         <f>G6</f>
         <v>0.111</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
@@ -1217,14 +1196,14 @@
       <c r="G7" s="13">
         <v>0.10100000000000001</v>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="9">
         <f t="shared" ref="H7:H17" si="1">G7</f>
         <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
-      <c r="B8" s="47" t="s">
+      <c r="A8" s="36"/>
+      <c r="B8" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
@@ -1243,14 +1222,14 @@
       <c r="G8" s="14">
         <v>0.115</v>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="33">
         <f t="shared" si="1"/>
         <v>0.115</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="42"/>
-      <c r="B9" s="47"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1252,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="42"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="17" t="s">
         <v>9</v>
       </c>
@@ -1297,8 +1276,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
@@ -1321,8 +1300,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="48"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="18" t="s">
         <v>11</v>
       </c>
@@ -1345,10 +1324,10 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="41" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="19" t="s">
@@ -1376,8 +1355,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="42"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1379,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="47"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="17" t="s">
         <v>9</v>
       </c>
@@ -1424,8 +1403,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="42"/>
-      <c r="B16" s="47"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="17" t="s">
         <v>10</v>
       </c>
@@ -1448,8 +1427,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="48"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="18" t="s">
         <v>11</v>
       </c>
@@ -1495,98 +1474,86 @@
     </row>
     <row r="21" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="E22" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="47"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="40" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="40"/>
+      <c r="F23" s="48"/>
       <c r="G23" s="23" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="44" t="s">
+      <c r="A24" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="5">
-        <v>4.0000000000000001E-3</v>
-      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="8">
         <f>E24</f>
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G24" s="11">
-        <v>2.7E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G24" s="11"/>
       <c r="H24" s="33">
         <f>G24</f>
-        <v>2.7E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="45"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="26">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="E25" s="21">
-        <v>1.2999999999999999E-2</v>
-      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="6">
         <f t="shared" ref="F25:F36" si="2">E25</f>
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="G25" s="12">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="H25" s="50">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="20">
         <f>G25</f>
-        <v>5.6000000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="46"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="18" t="s">
         <v>11</v>
       </c>
@@ -1597,40 +1564,34 @@
         <v>0</v>
       </c>
       <c r="G26" s="13"/>
-      <c r="H26" s="51">
+      <c r="H26" s="9">
         <f t="shared" ref="H26:H36" si="3">G26</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="42"/>
-      <c r="B27" s="47" t="s">
+      <c r="A27" s="36"/>
+      <c r="B27" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="5">
-        <v>2.1000000000000001E-2</v>
-      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="8">
         <f t="shared" si="2"/>
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G27" s="14">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="H27" s="49">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="33">
         <f t="shared" si="3"/>
-        <v>0.11600000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="42"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="17" t="s">
         <v>8</v>
       </c>
@@ -1647,82 +1608,64 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="B29" s="47"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2E-3</v>
-      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="6">
         <f t="shared" si="2"/>
-        <v>2E-3</v>
-      </c>
-      <c r="G29" s="15">
-        <v>1.7000000000000001E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G29" s="15"/>
       <c r="H29" s="10">
         <f t="shared" si="3"/>
-        <v>1.7000000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="36"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="30">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.01</v>
-      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="2"/>
       <c r="F30" s="6">
         <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="G30" s="15">
-        <v>4.3999999999999997E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" s="15"/>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
-        <v>4.3999999999999997E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="43"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="4">
-        <v>8.0000000000000002E-3</v>
-      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="7">
         <f t="shared" si="2"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G31" s="13">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="H31" s="51">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="9">
         <f t="shared" si="3"/>
-        <v>5.8999999999999997E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="41" t="s">
         <v>4</v>
       </c>
       <c r="C32" s="19" t="s">
@@ -1741,8 +1684,8 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="42"/>
-      <c r="B33" s="47"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="17" t="s">
         <v>8</v>
       </c>
@@ -1759,8 +1702,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="42"/>
-      <c r="B34" s="47"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="17" t="s">
         <v>9</v>
       </c>
@@ -1777,8 +1720,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="42"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="17" t="s">
         <v>10</v>
       </c>
@@ -1795,8 +1738,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="43"/>
-      <c r="B36" s="48"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="42"/>
       <c r="C36" s="18" t="s">
         <v>11</v>
       </c>
@@ -1814,28 +1757,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:H22"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
